--- a/EFPP_Termine.xlsx
+++ b/EFPP_Termine.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hochschulefresenius1-my.sharepoint.com/personal/caroline_zygar-hoffmann_charlotte-fresenius-uni_de/Documents/Lehre/EFPP/EFPP_Folien/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="277" documentId="13_ncr:1_{7895C6CF-6C22-436B-9E79-F7DD05ADAA21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA4C1A0E-E13A-43D9-A8C0-DD563A58E7AC}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{AAC49AE5-350D-49F4-973C-8611E9108AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD51212D-B017-4418-A527-E0D908CD3F7F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{403CBBCA-A596-E442-9191-812ECD39B1A7}"/>
+    <workbookView xWindow="1035" yWindow="1260" windowWidth="28800" windowHeight="15435" xr2:uid="{403CBBCA-A596-E442-9191-812ECD39B1A7}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="23">
   <si>
     <t>Datum</t>
   </si>
@@ -47,27 +47,9 @@
     <t>Freie Spitze und Fragen</t>
   </si>
   <si>
-    <t>Manifeste Merkmale: Verhaltensbeobachtung</t>
-  </si>
-  <si>
-    <t>Latente Merkmale: Befragungen, Tests</t>
-  </si>
-  <si>
-    <t>Bio-psychologische Methoden</t>
-  </si>
-  <si>
     <t>Psychologische Perspektiven und ihre Forschungsmethoden</t>
   </si>
   <si>
-    <t>Feiertag (Christi Himmelfahrt)</t>
-  </si>
-  <si>
-    <t>DIGITAL, DIENSTAG</t>
-  </si>
-  <si>
-    <t>Feiertag (Fronleichnam)</t>
-  </si>
-  <si>
     <t>Forschungsethik und Open Science</t>
   </si>
   <si>
@@ -80,30 +62,18 @@
     <t>Messen in der Psychologie</t>
   </si>
   <si>
-    <t>manifest, latent, quant, qual, Gütekriterien, TT</t>
-  </si>
-  <si>
     <t>Termin entfällt</t>
   </si>
   <si>
     <t>Kausalität, Experiment und Studiendesigns</t>
   </si>
   <si>
-    <t>DIGITAL, DONNERSTAG</t>
-  </si>
-  <si>
     <t>Psychologie als Wissenschaft Teil 2</t>
   </si>
   <si>
     <t>Psychologie als Wissenschaft Teil 1</t>
   </si>
   <si>
-    <t>Gastvortrag</t>
-  </si>
-  <si>
-    <t>rausgefallen: Statistische Herangehensweisen / Evaluationsforschung</t>
-  </si>
-  <si>
     <t>Qualitative Methoden: Verstehen des Einzelfalls Teil 1</t>
   </si>
   <si>
@@ -114,6 +84,27 @@
   </si>
   <si>
     <t>Einheit</t>
+  </si>
+  <si>
+    <t>Puffer oder Statistische Herangehensweisen / Evaluationsforschung</t>
+  </si>
+  <si>
+    <t>Verhaltensbeobachtung</t>
+  </si>
+  <si>
+    <t>Befragungen &amp; Tests</t>
+  </si>
+  <si>
+    <t>Gastvortag (Fokus: Forschung mit biopsychologischen Methoden)</t>
+  </si>
+  <si>
+    <t>Prüfungswoche (Termin entfällt)</t>
+  </si>
+  <si>
+    <t>Weihnachtspause (Termin entfällt)</t>
+  </si>
+  <si>
+    <t>Debattierclub?</t>
   </si>
 </sst>
 </file>
@@ -123,7 +114,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d\.m\.yy"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -159,13 +150,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF0070C0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -174,7 +158,6 @@
       <sz val="12"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -197,7 +180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -207,11 +190,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -227,10 +209,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -530,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38C9749B-DB69-4840-8C47-7993253605D0}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="65.625" customWidth="1"/>
@@ -540,9 +518,9 @@
     <col min="12" max="12" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -551,217 +529,229 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>45393</v>
+        <v>45581</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="5">
-        <v>45398</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B3" s="6">
+        <v>45588</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" s="1">
-        <v>45407</v>
+        <v>45595</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" s="1">
-        <v>45414</v>
+        <v>45602</v>
       </c>
       <c r="C5" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="3">
-        <v>45421</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="6">
+        <v>45609</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>4</v>
-      </c>
-      <c r="B7" s="5">
-        <v>45428</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1">
+        <v>45616</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
       <c r="B8" s="1">
-        <v>45435</v>
-      </c>
-      <c r="C8" t="s">
-        <v>5</v>
+        <v>45623</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="D8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="3">
+        <v>45630</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="3">
-        <v>45442</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>9</v>
-      </c>
       <c r="D9" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>6</v>
       </c>
       <c r="B10" s="1">
-        <v>45449</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>45637</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="5"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B11" s="1">
-        <v>45456</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>23</v>
+        <v>45644</v>
+      </c>
+      <c r="C11" t="s">
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="3">
+        <v>45651</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="3">
+        <v>45658</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>8</v>
+      </c>
+      <c r="B14" s="1">
+        <v>45665</v>
+      </c>
+      <c r="C14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>9</v>
+      </c>
+      <c r="B15" s="1">
+        <v>45672</v>
+      </c>
+      <c r="C15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>10</v>
+      </c>
+      <c r="B16" s="1">
+        <v>45679</v>
+      </c>
+      <c r="C16" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="5"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17">
         <v>11</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>7</v>
-      </c>
-      <c r="B12" s="1">
-        <v>45463</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B17" s="1">
+        <v>45686</v>
+      </c>
+      <c r="C17" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>8</v>
-      </c>
-      <c r="B13" s="1">
-        <v>45470</v>
-      </c>
-      <c r="C13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>9</v>
-      </c>
-      <c r="B14" s="1">
-        <v>45477</v>
-      </c>
-      <c r="C14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>10</v>
-      </c>
-      <c r="B15" s="1">
-        <v>45484</v>
-      </c>
-      <c r="C15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>11</v>
-      </c>
-      <c r="B16" s="1">
-        <v>45491</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="D17" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>12</v>
+      </c>
+      <c r="B18" s="1">
+        <v>45693</v>
+      </c>
+      <c r="C18" t="s">
         <v>2</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/EFPP_Termine.xlsx
+++ b/EFPP_Termine.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hochschulefresenius1-my.sharepoint.com/personal/caroline_zygar-hoffmann_charlotte-fresenius-uni_de/Documents/Lehre/EFPP/EFPP_Folien/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{AAC49AE5-350D-49F4-973C-8611E9108AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD51212D-B017-4418-A527-E0D908CD3F7F}"/>
+  <xr:revisionPtr revIDLastSave="103" documentId="13_ncr:1_{AAC49AE5-350D-49F4-973C-8611E9108AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{777FE798-6E4A-4D1D-AF55-BD70CB4EC769}"/>
   <bookViews>
-    <workbookView xWindow="1035" yWindow="1260" windowWidth="28800" windowHeight="15435" xr2:uid="{403CBBCA-A596-E442-9191-812ECD39B1A7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{403CBBCA-A596-E442-9191-812ECD39B1A7}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
   <si>
     <t>Datum</t>
   </si>
@@ -50,18 +50,12 @@
     <t>Psychologische Perspektiven und ihre Forschungsmethoden</t>
   </si>
   <si>
-    <t>Forschungsethik und Open Science</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
     <t>Anmerkung</t>
   </si>
   <si>
-    <t>Messen in der Psychologie</t>
-  </si>
-  <si>
     <t>Termin entfällt</t>
   </si>
   <si>
@@ -74,37 +68,40 @@
     <t>Psychologie als Wissenschaft Teil 1</t>
   </si>
   <si>
-    <t>Qualitative Methoden: Verstehen des Einzelfalls Teil 1</t>
-  </si>
-  <si>
-    <t>Qualitative Methoden: Verstehen des Einzelfalls Teil 2</t>
-  </si>
-  <si>
-    <t>Digitale Messmethoden, Big Data und Machine-Learning</t>
-  </si>
-  <si>
     <t>Einheit</t>
   </si>
   <si>
     <t>Puffer oder Statistische Herangehensweisen / Evaluationsforschung</t>
   </si>
   <si>
-    <t>Verhaltensbeobachtung</t>
+    <t>Gastvortag (Fokus: Forschung mit biopsychologischen Methoden)</t>
+  </si>
+  <si>
+    <t>Feiertag (Termin entfällt)</t>
+  </si>
+  <si>
+    <t>Prüfungswoche / Feiertag (Termin entfällt)</t>
+  </si>
+  <si>
+    <t>Wegen Krankheit entfallen</t>
+  </si>
+  <si>
+    <t>Qualitative Methoden: Verstehen des Einzelfalls</t>
+  </si>
+  <si>
+    <t>Messen in der Psychologie Teil 1</t>
   </si>
   <si>
     <t>Befragungen &amp; Tests</t>
   </si>
   <si>
-    <t>Gastvortag (Fokus: Forschung mit biopsychologischen Methoden)</t>
-  </si>
-  <si>
-    <t>Prüfungswoche (Termin entfällt)</t>
-  </si>
-  <si>
-    <t>Weihnachtspause (Termin entfällt)</t>
-  </si>
-  <si>
-    <t>Debattierclub?</t>
+    <t>Messen in der Psychologie Teil 2</t>
+  </si>
+  <si>
+    <t>Forschungsethik und Open Science + Digitale Messmethoden, Ambulatory Assessment und Machine-Learning</t>
+  </si>
+  <si>
+    <t>Messen in der Psychologie Teil 3 + Verhaltensbeobachtung</t>
   </si>
 </sst>
 </file>
@@ -209,6 +206,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -508,10 +509,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38C9749B-DB69-4840-8C47-7993253605D0}">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="65.625" customWidth="1"/>
+    <col min="3" max="3" width="91.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27" customWidth="1"/>
     <col min="10" max="10" width="21.625" customWidth="1"/>
     <col min="11" max="11" width="16.125" customWidth="1"/>
@@ -520,7 +521,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -529,7 +530,7 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -537,13 +538,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>45581</v>
+        <v>45757</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -551,142 +552,136 @@
         <v>1</v>
       </c>
       <c r="B3" s="6">
-        <v>45588</v>
+        <v>45764</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1">
-        <v>45595</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3">
+        <v>45771</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1">
-        <v>45602</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3">
+        <v>45778</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" s="6">
-        <v>45609</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>18</v>
+        <v>2</v>
+      </c>
+      <c r="B6" s="1">
+        <v>45785</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1">
-        <v>45616</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>12</v>
+        <v>3</v>
+      </c>
+      <c r="B7" s="6">
+        <v>45792</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" s="1">
-        <v>45623</v>
+        <v>45799</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" s="3">
-        <v>45630</v>
+        <v>45806</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" s="1">
-        <v>45637</v>
+        <v>45813</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="5"/>
+        <v>12</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" s="1">
-        <v>45644</v>
+        <v>45820</v>
       </c>
       <c r="C11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>5</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="D11" s="5"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B12" s="3">
-        <v>45651</v>
+        <v>45827</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="3">
-        <v>45658</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>21</v>
+      <c r="A13">
+        <v>7</v>
+      </c>
+      <c r="B13" s="1">
+        <v>45834</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -694,13 +689,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="1">
-        <v>45665</v>
-      </c>
-      <c r="C14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>5</v>
+        <v>45841</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -708,13 +700,13 @@
         <v>9</v>
       </c>
       <c r="B15" s="1">
-        <v>45672</v>
+        <v>45848</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -722,36 +714,27 @@
         <v>10</v>
       </c>
       <c r="B16" s="1">
-        <v>45679</v>
+        <v>45855</v>
       </c>
       <c r="C16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="5"/>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="1"/>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="1"/>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="5"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17">
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
         <v>11</v>
-      </c>
-      <c r="B17" s="1">
-        <v>45686</v>
-      </c>
-      <c r="C17" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>12</v>
-      </c>
-      <c r="B18" s="1">
-        <v>45693</v>
-      </c>
-      <c r="C18" t="s">
-        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/EFPP_Termine.xlsx
+++ b/EFPP_Termine.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hochschulefresenius1-my.sharepoint.com/personal/caroline_zygar-hoffmann_charlotte-fresenius-uni_de/Documents/Lehre/EFPP/EFPP_Folien/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="103" documentId="13_ncr:1_{AAC49AE5-350D-49F4-973C-8611E9108AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{777FE798-6E4A-4D1D-AF55-BD70CB4EC769}"/>
+  <xr:revisionPtr revIDLastSave="189" documentId="13_ncr:1_{AAC49AE5-350D-49F4-973C-8611E9108AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6E3E8DD-1F58-4198-9EF0-CAEE99B4E1E5}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{403CBBCA-A596-E442-9191-812ECD39B1A7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{403CBBCA-A596-E442-9191-812ECD39B1A7}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
   <si>
     <t>Datum</t>
   </si>
@@ -56,9 +56,6 @@
     <t>Anmerkung</t>
   </si>
   <si>
-    <t>Termin entfällt</t>
-  </si>
-  <si>
     <t>Kausalität, Experiment und Studiendesigns</t>
   </si>
   <si>
@@ -80,12 +77,6 @@
     <t>Feiertag (Termin entfällt)</t>
   </si>
   <si>
-    <t>Prüfungswoche / Feiertag (Termin entfällt)</t>
-  </si>
-  <si>
-    <t>Wegen Krankheit entfallen</t>
-  </si>
-  <si>
     <t>Qualitative Methoden: Verstehen des Einzelfalls</t>
   </si>
   <si>
@@ -98,10 +89,19 @@
     <t>Messen in der Psychologie Teil 2</t>
   </si>
   <si>
-    <t>Forschungsethik und Open Science + Digitale Messmethoden, Ambulatory Assessment und Machine-Learning</t>
-  </si>
-  <si>
-    <t>Messen in der Psychologie Teil 3 + Verhaltensbeobachtung</t>
+    <t>Verhaltensbeobachtung</t>
+  </si>
+  <si>
+    <t>Weihnachtspause (Termin entfällt)</t>
+  </si>
+  <si>
+    <t>Forschungsethik und Open Science</t>
+  </si>
+  <si>
+    <t>Digitale Messmethoden, Ambulatory Assessment und Machine-Learning</t>
+  </si>
+  <si>
+    <t>Zeitraum Wiederholungsprüfung (Termin entfällt)</t>
   </si>
 </sst>
 </file>
@@ -177,7 +177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -191,6 +191,7 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -206,10 +207,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -509,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38C9749B-DB69-4840-8C47-7993253605D0}">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="91.375" bestFit="1" customWidth="1"/>
@@ -521,7 +518,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -538,60 +535,54 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>45757</v>
+        <v>45944</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>4</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" s="6">
-        <v>45764</v>
+        <v>45951</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="3">
-        <v>45771</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>4</v>
-      </c>
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="6">
+        <v>45958</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3">
-        <v>45778</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" s="6">
+        <v>45965</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" s="1">
-        <v>45785</v>
+        <v>45972</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -599,111 +590,106 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7" s="6">
-        <v>45792</v>
+        <v>45979</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" s="1">
+        <v>45986</v>
+      </c>
+      <c r="C8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="1">
-        <v>45799</v>
-      </c>
-      <c r="C8" s="5" t="s">
+      <c r="B9" s="3">
+        <v>45993</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="3">
-        <v>45806</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="D9" s="2"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B10" s="1">
-        <v>45813</v>
+        <v>46000</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B11" s="1">
-        <v>45820</v>
-      </c>
-      <c r="C11" t="s">
+        <v>46007</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="5"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="3">
+        <v>46014</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="5"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="3">
-        <v>45827</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>7</v>
-      </c>
-      <c r="B13" s="1">
-        <v>45834</v>
-      </c>
-      <c r="C13" t="s">
-        <v>7</v>
+      <c r="B13" s="3">
+        <v>46021</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>8</v>
-      </c>
-      <c r="B14" s="1">
-        <v>45841</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>16</v>
+      <c r="A14" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="3">
+        <v>46028</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B15" s="1">
-        <v>45848</v>
+        <v>46035</v>
       </c>
       <c r="C15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>4</v>
@@ -711,30 +697,41 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16">
+        <v>9</v>
+      </c>
+      <c r="B16" s="1">
+        <v>46042</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="5"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17">
         <v>10</v>
       </c>
-      <c r="B16" s="1">
-        <v>45855</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="B17" s="1">
+        <v>46049</v>
+      </c>
+      <c r="C17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>11</v>
+      </c>
+      <c r="B18" s="1">
+        <v>46056</v>
+      </c>
+      <c r="C18" t="s">
         <v>2</v>
       </c>
-      <c r="D16" s="5"/>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="1"/>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="1"/>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C23" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
